--- a/exports/TATASTEEL_full_report.xlsx
+++ b/exports/TATASTEEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.4</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>110.86</v>
+        <v>105.73</v>
       </c>
       <c r="I2" t="n">
         <v>109.6729316572768</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>0.22</v>
+        <v>-4.42</v>
       </c>
       <c r="L2" t="n">
-        <v>4.85</v>
+        <v>5.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="N2" t="n">
-        <v>3.36</v>
+        <v>6.12</v>
       </c>
       <c r="O2" t="n">
         <v>0.89</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>10.15</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44594.55208333334</v>
+        <v>44595.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>110.62</v>
+        <v>111.4</v>
       </c>
       <c r="I3" t="n">
         <v>110.7906657350608</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.62</v>
+        <v>-5.36</v>
       </c>
       <c r="L3" t="n">
-        <v>5.73</v>
+        <v>5.87</v>
       </c>
       <c r="M3" t="n">
         <v>2.28</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.55208333334</v>
+        <v>44607.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>112.09</v>
+        <v>110.28</v>
       </c>
       <c r="I4" t="n">
         <v>111.5506557256227</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>0.62</v>
+        <v>-1.01</v>
       </c>
       <c r="L4" t="n">
         <v>2.59</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.17</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44617.55208333334</v>
+        <v>44620.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>108.23</v>
+        <v>114.72</v>
       </c>
       <c r="I5" t="n">
         <v>111.4038144382421</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>1.86</v>
+        <v>-4.03</v>
       </c>
       <c r="L5" t="n">
         <v>4.74</v>
@@ -726,7 +785,7 @@
         <v>1.78</v>
       </c>
       <c r="N5" t="n">
-        <v>6.19</v>
+        <v>6.68</v>
       </c>
       <c r="O5" t="n">
         <v>1.92</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>12.86</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44662.55208333334</v>
+        <v>44663.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>128.85</v>
+        <v>123.81</v>
       </c>
       <c r="I6" t="n">
         <v>123.970024391643</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K6" t="n">
-        <v>12.32</v>
+        <v>7.92</v>
       </c>
       <c r="L6" t="n">
         <v>6.9</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.17</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44685.55208333334</v>
+        <v>44686.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>120.2</v>
+        <v>124.06</v>
       </c>
       <c r="I7" t="n">
         <v>123.594895131105</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
-        <v>2.92</v>
+        <v>-0.2</v>
       </c>
       <c r="L7" t="n">
         <v>5.02</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>8.44</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44690.55208333334</v>
+        <v>44691.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>118.73</v>
+        <v>112.67</v>
       </c>
       <c r="I8" t="n">
         <v>113.6111193513574</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.3</v>
+        <v>-9.18</v>
       </c>
       <c r="L8" t="n">
-        <v>4.93</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>2.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>7.24</v>
       </c>
       <c r="O8" t="n">
         <v>1.79</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.52</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44749.38541666666</v>
+        <v>44749.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>81.3</v>
+        <v>85.02</v>
       </c>
       <c r="I9" t="n">
         <v>84.9259283480213</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>58</v>
+        <v>58.16666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>27.84</v>
+        <v>24.54</v>
       </c>
       <c r="L9" t="n">
         <v>5.68</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.76</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>103.73</v>
+        <v>100.9</v>
       </c>
       <c r="I10" t="n">
         <v>101.8367282189481</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K10" t="n">
-        <v>22.01</v>
+        <v>18.68</v>
       </c>
       <c r="L10" t="n">
         <v>5.12</v>
@@ -1011,7 +1130,7 @@
         <v>0.91</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>4.29</v>
       </c>
       <c r="O10" t="n">
         <v>5.72</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.63</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>95.56999999999999</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>97.24678942938941</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K11" t="n">
-        <v>5.28</v>
+        <v>3.44</v>
       </c>
       <c r="L11" t="n">
         <v>3.44</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.88</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44904.38541666666</v>
+        <v>44904.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>105.2</v>
+        <v>104.32</v>
       </c>
       <c r="I12" t="n">
         <v>104.7210566130172</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>64</v>
+        <v>64.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>7.97</v>
+        <v>7.07</v>
       </c>
       <c r="L12" t="n">
         <v>5.21</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>4.97</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44921.55208333334</v>
+        <v>44922.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>98.98999999999999</v>
+        <v>103.93</v>
       </c>
       <c r="I13" t="n">
         <v>103.3774422738375</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>5.11</v>
+        <v>0.37</v>
       </c>
       <c r="L13" t="n">
         <v>2.9</v>
       </c>
       <c r="M13" t="n">
-        <v>0.74</v>
+        <v>1.73</v>
       </c>
       <c r="N13" t="n">
-        <v>2.69</v>
+        <v>6.32</v>
       </c>
       <c r="O13" t="n">
         <v>-1.43</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.73</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44953.55208333334</v>
+        <v>44956.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>114.14</v>
+        <v>111.6</v>
       </c>
       <c r="I14" t="n">
         <v>111.8795871891832</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K14" t="n">
-        <v>9.82</v>
+        <v>7.38</v>
       </c>
       <c r="L14" t="n">
         <v>3.81</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.61</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45026.55208333334</v>
+        <v>45027.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>99.19</v>
+        <v>100.36</v>
       </c>
       <c r="I15" t="n">
         <v>100.0725483917706</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>70.16666666666667</v>
+        <v>71</v>
       </c>
       <c r="K15" t="n">
-        <v>11.12</v>
+        <v>10.07</v>
       </c>
       <c r="L15" t="n">
         <v>5.51</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>3.86</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45057.55208333334</v>
+        <v>45058.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>102.66</v>
+        <v>101.04</v>
       </c>
       <c r="I16" t="n">
         <v>101.3212240577757</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K16" t="n">
-        <v>2.29</v>
+        <v>0.68</v>
       </c>
       <c r="L16" t="n">
         <v>1.17</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>3.96</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>100.51</v>
+        <v>102.51</v>
       </c>
       <c r="I17" t="n">
         <v>101.4612628602642</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K17" t="n">
-        <v>0.52</v>
+        <v>-1.45</v>
       </c>
       <c r="L17" t="n">
         <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>1.84</v>
       </c>
       <c r="O17" t="n">
         <v>-1.67</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.05</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>105.15</v>
+        <v>104.32</v>
       </c>
       <c r="I18" t="n">
         <v>104.7101955344416</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K18" t="n">
-        <v>2.58</v>
+        <v>1.77</v>
       </c>
       <c r="L18" t="n">
         <v>2.76</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>3.81</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45114.55208333334</v>
+        <v>45117.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>105.59</v>
+        <v>108.18</v>
       </c>
       <c r="I19" t="n">
         <v>107.1997858180734</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.22</v>
+        <v>-3.7</v>
       </c>
       <c r="L19" t="n">
-        <v>3.65</v>
+        <v>3.98</v>
       </c>
       <c r="M19" t="n">
         <v>0.75</v>
       </c>
       <c r="N19" t="n">
-        <v>1.15</v>
+        <v>3.33</v>
       </c>
       <c r="O19" t="n">
         <v>-1.82</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>4.79</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45140.55208333334</v>
+        <v>45141.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>112.97</v>
+        <v>111.65</v>
       </c>
       <c r="I20" t="n">
         <v>112.3336428471869</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K20" t="n">
-        <v>4.43</v>
+        <v>3.21</v>
       </c>
       <c r="L20" t="n">
         <v>2.39</v>
       </c>
       <c r="M20" t="n">
-        <v>0.27</v>
+        <v>0.43</v>
       </c>
       <c r="N20" t="n">
         <v>3.34</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>5.48</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45167.55208333334</v>
+        <v>45168.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>113.55</v>
+        <v>116.09</v>
       </c>
       <c r="I21" t="n">
         <v>114.0715874753115</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7</v>
+        <v>-3.98</v>
       </c>
       <c r="L21" t="n">
-        <v>3.11</v>
+        <v>4.25</v>
       </c>
       <c r="M21" t="n">
         <v>0.84</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>4.24</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45202.55208333334</v>
+        <v>45203.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>121.66</v>
+        <v>118.58</v>
       </c>
       <c r="I22" t="n">
         <v>119.3214917572538</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K22" t="n">
-        <v>4.8</v>
+        <v>2.14</v>
       </c>
       <c r="L22" t="n">
         <v>1.81</v>
       </c>
       <c r="M22" t="n">
-        <v>0.61</v>
+        <v>0.88</v>
       </c>
       <c r="N22" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="O22" t="n">
         <v>1.94</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.42</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>114.53</v>
+        <v>117.17</v>
       </c>
       <c r="I23" t="n">
         <v>115.3010732276353</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K23" t="n">
-        <v>3.42</v>
+        <v>1.19</v>
       </c>
       <c r="L23" t="n">
         <v>3.09</v>
@@ -1752,7 +2027,7 @@
         <v>1.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2.08</v>
+        <v>2.81</v>
       </c>
       <c r="O23" t="n">
         <v>-2.17</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>126.79</v>
+        <v>122.44</v>
       </c>
       <c r="I24" t="n">
         <v>125.1025894001054</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K24" t="n">
-        <v>8.210000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
         <v>1.67</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>6.93</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45286.55208333334</v>
+        <v>45287.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>128.85</v>
+        <v>130.12</v>
       </c>
       <c r="I25" t="n">
         <v>129.4643444851318</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.24</v>
+        <v>-6.27</v>
       </c>
       <c r="L25" t="n">
-        <v>5.75</v>
+        <v>7.99</v>
       </c>
       <c r="M25" t="n">
         <v>0.96</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>4.82</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45296.38541666666</v>
+        <v>45296.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>127.67</v>
+        <v>127.18</v>
       </c>
       <c r="I26" t="n">
         <v>127.4740453707625</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.88</v>
+        <v>-2.26</v>
       </c>
       <c r="L26" t="n">
-        <v>2.29</v>
+        <v>2.94</v>
       </c>
       <c r="M26" t="n">
         <v>-0</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>4.74</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45324.38541666666</v>
+        <v>45324.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>130.6</v>
+        <v>132.12</v>
       </c>
       <c r="I27" t="n">
         <v>130.7600047483542</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.69</v>
+        <v>-3.88</v>
       </c>
       <c r="L27" t="n">
-        <v>3.66</v>
+        <v>4.5</v>
       </c>
       <c r="M27" t="n">
         <v>1.2</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>5.22</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45334.38541666666</v>
+        <v>45334.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>131.43</v>
+        <v>130.9</v>
       </c>
       <c r="I28" t="n">
         <v>131.1540367611948</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.52</v>
+        <v>-0.92</v>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="M28" t="n">
         <v>0.07000000000000001</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>6.45</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45342.55208333334</v>
+        <v>45343.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>134.56</v>
+        <v>138.37</v>
       </c>
       <c r="I29" t="n">
         <v>138.1962044737211</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.8</v>
+        <v>-5.71</v>
       </c>
       <c r="L29" t="n">
-        <v>4.4</v>
+        <v>6.46</v>
       </c>
       <c r="M29" t="n">
         <v>0.65</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.21</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>145.31</v>
+        <v>139.4</v>
       </c>
       <c r="I30" t="n">
         <v>141.3025822438309</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K30" t="n">
-        <v>5.02</v>
+        <v>0.74</v>
       </c>
       <c r="L30" t="n">
         <v>4.09</v>
@@ -2151,7 +2510,7 @@
         <v>0.14</v>
       </c>
       <c r="N30" t="n">
-        <v>2.63</v>
+        <v>6.01</v>
       </c>
       <c r="O30" t="n">
         <v>1.89</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.49</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45372.55208333334</v>
+        <v>45373.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>143.11</v>
+        <v>145.26</v>
       </c>
       <c r="I31" t="n">
         <v>145.1802715691441</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.66</v>
+        <v>-4.2</v>
       </c>
       <c r="L31" t="n">
         <v>4.66</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>8.76</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>166.52</v>
+        <v>159.04</v>
       </c>
       <c r="I32" t="n">
         <v>160.1458501480035</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>68.16666666666667</v>
+        <v>69</v>
       </c>
       <c r="K32" t="n">
-        <v>14.64</v>
+        <v>9.49</v>
       </c>
       <c r="L32" t="n">
         <v>2.62</v>
       </c>
       <c r="M32" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="N32" t="n">
-        <v>2.7</v>
+        <v>5.16</v>
       </c>
       <c r="O32" t="n">
         <v>0.96</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.61</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>164.71</v>
+        <v>171.06</v>
       </c>
       <c r="I33" t="n">
         <v>170.5879031753943</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.57</v>
+        <v>-7.56</v>
       </c>
       <c r="L33" t="n">
-        <v>5.31</v>
+        <v>7.99</v>
       </c>
       <c r="M33" t="n">
         <v>3.51</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>12.05</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45482.55208333334</v>
+        <v>45483.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>168.02</v>
+        <v>164.56</v>
       </c>
       <c r="I34" t="n">
         <v>167.7942772271526</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.78</v>
+        <v>-3.8</v>
       </c>
       <c r="L34" t="n">
-        <v>4.48</v>
+        <v>4.59</v>
       </c>
       <c r="M34" t="n">
         <v>1.09</v>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="O34" t="n">
         <v>4.03</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>4.97</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45504.38541666666</v>
+        <v>45504.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>161.18</v>
+        <v>161.63</v>
       </c>
       <c r="I35" t="n">
         <v>161.6249432318776</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="L35" t="n">
         <v>2.67</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>4.8</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>154.78</v>
+        <v>147.52</v>
       </c>
       <c r="I36" t="n">
         <v>153.8672865551653</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.24</v>
+        <v>-8.73</v>
       </c>
       <c r="L36" t="n">
-        <v>6.46</v>
+        <v>9.92</v>
       </c>
       <c r="M36" t="n">
-        <v>1.24</v>
+        <v>2.98</v>
       </c>
       <c r="N36" t="n">
-        <v>2.84</v>
+        <v>5.71</v>
       </c>
       <c r="O36" t="n">
         <v>0.52</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45530.38541666666</v>
+        <v>45530.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>151.37</v>
+        <v>152.35</v>
       </c>
       <c r="I37" t="n">
         <v>151.4010238373369</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.61</v>
+        <v>-3.27</v>
       </c>
       <c r="L37" t="n">
-        <v>3.14</v>
+        <v>3.61</v>
       </c>
       <c r="M37" t="n">
         <v>1.68</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>4.09</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>147.8</v>
+        <v>145.94</v>
       </c>
       <c r="I38" t="n">
         <v>146.3098400321297</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.99</v>
+        <v>-4.21</v>
       </c>
       <c r="L38" t="n">
-        <v>4.33</v>
+        <v>5.03</v>
       </c>
       <c r="M38" t="n">
         <v>1.83</v>
       </c>
       <c r="N38" t="n">
-        <v>0.77</v>
+        <v>1.16</v>
       </c>
       <c r="O38" t="n">
         <v>1.06</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>3.87</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45548.55208333334</v>
+        <v>45551.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>149.9</v>
+        <v>150.87</v>
       </c>
       <c r="I39" t="n">
         <v>150.7603089286529</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.71</v>
+        <v>-3.38</v>
       </c>
       <c r="L39" t="n">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="M39" t="n">
         <v>2.44</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>4.18</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45572.55208333334</v>
+        <v>45573.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>160.3</v>
+        <v>156.16</v>
       </c>
       <c r="I40" t="n">
         <v>157.2176035168144</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K40" t="n">
-        <v>6.25</v>
+        <v>3.51</v>
       </c>
       <c r="L40" t="n">
         <v>4.28</v>
@@ -2721,7 +3200,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>1.73</v>
+        <v>2.53</v>
       </c>
       <c r="O40" t="n">
         <v>0.52</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>6.66</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>148.93</v>
+        <v>149.8</v>
       </c>
       <c r="I41" t="n">
         <v>149.6842131507034</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K41" t="n">
-        <v>4.63</v>
+        <v>4.07</v>
       </c>
       <c r="L41" t="n">
         <v>2.49</v>
       </c>
       <c r="M41" t="n">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="N41" t="n">
         <v>3.6</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.34</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45607.55208333334</v>
+        <v>45608.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>141.98</v>
+        <v>141.62</v>
       </c>
       <c r="I42" t="n">
         <v>141.9091933111907</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.22</v>
+        <v>-5.46</v>
       </c>
       <c r="L42" t="n">
         <v>5.99</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.48</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45628.38541666666</v>
+        <v>45628.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>141.86</v>
+        <v>143.02</v>
       </c>
       <c r="I43" t="n">
         <v>142.7031729137181</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.17</v>
+        <v>-0.99</v>
       </c>
       <c r="L43" t="n">
         <v>1.53</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>4.4</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>142.33</v>
+        <v>140.5</v>
       </c>
       <c r="I44" t="n">
         <v>141.9257038098391</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.48</v>
+        <v>-1.76</v>
       </c>
       <c r="L44" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
         <v>0.27</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.44</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>127.18</v>
+        <v>128.23</v>
       </c>
       <c r="I45" t="n">
         <v>127.2901235961713</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K45" t="n">
-        <v>9.48</v>
+        <v>8.73</v>
       </c>
       <c r="L45" t="n">
         <v>2.17</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.52</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>150.34</v>
+        <v>138.86</v>
       </c>
       <c r="I46" t="n">
         <v>148.945339722811</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>73.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K46" t="n">
-        <v>17.24</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L46" t="n">
         <v>4.94</v>
@@ -3063,7 +3614,7 @@
         <v>1.7</v>
       </c>
       <c r="N46" t="n">
-        <v>3.07</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O46" t="n">
         <v>1.01</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.25</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>134.11</v>
+        <v>136.38</v>
       </c>
       <c r="I47" t="n">
         <v>136.3687434745322</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K47" t="n">
-        <v>3.42</v>
+        <v>1.79</v>
       </c>
       <c r="L47" t="n">
         <v>7.66</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.75</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>153.8</v>
+        <v>152.6</v>
       </c>
       <c r="I48" t="n">
         <v>153.4916552218904</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>12.77</v>
+        <v>11.89</v>
       </c>
       <c r="L48" t="n">
         <v>1.8</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>3.81</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45832.55208333334</v>
+        <v>45833.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>155.03</v>
+        <v>156.71</v>
       </c>
       <c r="I49" t="n">
         <v>156.5358751049105</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.59</v>
+        <v>-2.69</v>
       </c>
       <c r="L49" t="n">
         <v>2.86</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>4.09</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45846.55208333334</v>
+        <v>45847.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>161.9</v>
+        <v>158.21</v>
       </c>
       <c r="I50" t="n">
         <v>160.4324628802875</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K50" t="n">
-        <v>3.31</v>
+        <v>0.96</v>
       </c>
       <c r="L50" t="n">
         <v>0.77</v>
@@ -3291,7 +3890,7 @@
         <v>0.19</v>
       </c>
       <c r="N50" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="O50" t="n">
         <v>0.84</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>5.36</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45856.55208333334</v>
+        <v>45859.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>162.5</v>
+        <v>162.81</v>
       </c>
       <c r="I51" t="n">
         <v>162.754742523338</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.71</v>
+        <v>-2.91</v>
       </c>
       <c r="L51" t="n">
-        <v>2.87</v>
+        <v>4.67</v>
       </c>
       <c r="M51" t="n">
         <v>0.5</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>2.78</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45869.38541666666</v>
+        <v>45869.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>160.67</v>
+        <v>157.3</v>
       </c>
       <c r="I52" t="n">
         <v>158.7046079211849</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.31</v>
+        <v>-3.38</v>
       </c>
       <c r="L52" t="n">
-        <v>2.83</v>
+        <v>3.84</v>
       </c>
       <c r="M52" t="n">
         <v>0.72</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>4.72</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45876.38541666666</v>
+        <v>45876.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>156.54</v>
+        <v>159.83</v>
       </c>
       <c r="I53" t="n">
         <v>159.7372852820817</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K53" t="n">
-        <v>0.48</v>
+        <v>-1.61</v>
       </c>
       <c r="L53" t="n">
         <v>2.17</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>5.42</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45895.38541666666</v>
+        <v>45895.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>156.3</v>
+        <v>155.05</v>
       </c>
       <c r="I54" t="n">
         <v>155.6919193683894</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.21</v>
+        <v>-2.99</v>
       </c>
       <c r="L54" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="M54" t="n">
         <v>0.63</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>4.17</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45902.55208333334</v>
+        <v>45903.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>158.45</v>
+        <v>166.9</v>
       </c>
       <c r="I55" t="n">
         <v>159.53144623218</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.19</v>
+        <v>-7.64</v>
       </c>
       <c r="L55" t="n">
-        <v>2.59</v>
+        <v>7.77</v>
       </c>
       <c r="M55" t="n">
         <v>0.47</v>
       </c>
       <c r="N55" t="n">
-        <v>1.44</v>
+        <v>5.92</v>
       </c>
       <c r="O55" t="n">
         <v>-2.88</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.04</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>168.55</v>
+        <v>167.36</v>
       </c>
       <c r="I56" t="n">
         <v>168.2262060478659</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>0.99</v>
+        <v>0.28</v>
       </c>
       <c r="L56" t="n">
         <v>5.09</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>4.27</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45931.55208333334</v>
+        <v>45933.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>167.55</v>
+        <v>173.87</v>
       </c>
       <c r="I57" t="n">
         <v>173.4754567046142</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>5</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.11</v>
+        <v>-3.89</v>
       </c>
       <c r="L57" t="n">
-        <v>1.74</v>
+        <v>4.41</v>
       </c>
       <c r="M57" t="n">
-        <v>0.14</v>
+        <v>0.34</v>
       </c>
       <c r="N57" t="n">
-        <v>1.16</v>
+        <v>3.49</v>
       </c>
       <c r="O57" t="n">
         <v>-2.87</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.81</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>179.35</v>
+        <v>177.57</v>
       </c>
       <c r="I58" t="n">
         <v>177.9452909050024</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K58" t="n">
-        <v>3.15</v>
+        <v>2.13</v>
       </c>
       <c r="L58" t="n">
         <v>3.31</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>4.6</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46002.55208333334</v>
+        <v>46003.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>166.4</v>
+        <v>171.43</v>
       </c>
       <c r="I59" t="n">
         <v>167.1631145491794</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K59" t="n">
-        <v>6.29</v>
+        <v>3.46</v>
       </c>
       <c r="L59" t="n">
         <v>3.62</v>
@@ -3804,7 +4511,7 @@
         <v>2.99</v>
       </c>
       <c r="N59" t="n">
-        <v>2.72</v>
+        <v>3.37</v>
       </c>
       <c r="O59" t="n">
         <v>-1.12</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.49</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>179.9</v>
+        <v>178.98</v>
       </c>
       <c r="I60" t="n">
         <v>179.7276591099327</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K60" t="n">
-        <v>4.94</v>
+        <v>4.4</v>
       </c>
       <c r="L60" t="n">
         <v>2.35</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.11</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46035.55208333334</v>
+        <v>46036.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>182.45</v>
+        <v>189.08</v>
       </c>
       <c r="I61" t="n">
         <v>186.0407881674624</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.94</v>
+        <v>-5.64</v>
       </c>
       <c r="L61" t="n">
-        <v>3.02</v>
+        <v>6.52</v>
       </c>
       <c r="M61" t="n">
         <v>0.11</v>
       </c>
       <c r="N61" t="n">
-        <v>2.58</v>
+        <v>3.66</v>
       </c>
       <c r="O61" t="n">
         <v>-0.67</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.82</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46052.55208333334</v>
+        <v>46054.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>192.6</v>
+        <v>189.22</v>
       </c>
       <c r="I62" t="n">
         <v>190.1423516355199</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K62" t="n">
-        <v>1.86</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L62" t="n">
         <v>4.34</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>7.36</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46059.55208333334</v>
+        <v>46062.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>196.5</v>
+        <v>202.02</v>
       </c>
       <c r="I63" t="n">
         <v>198.6497583827419</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.85</v>
+        <v>-6.76</v>
       </c>
       <c r="L63" t="n">
-        <v>5.17</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M63" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="N63" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="O63" t="n">
         <v>-3.53</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>7.03</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>211</v>
+        <v>196.21</v>
       </c>
       <c r="I64" t="n">
         <v>205.0847241078313</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K64" t="n">
-        <v>4.45</v>
+        <v>-2.88</v>
       </c>
       <c r="L64" t="n">
-        <v>2.21</v>
+        <v>3.76</v>
       </c>
       <c r="M64" t="n">
         <v>3.49</v>
       </c>
       <c r="N64" t="n">
-        <v>2.4</v>
+        <v>7.08</v>
       </c>
       <c r="O64" t="n">
         <v>2.49</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.22</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46119.38541666666</v>
+        <v>46119.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>195.85</v>
+        <v>198</v>
       </c>
       <c r="I65" t="n">
         <v>197.5721613540125</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K65" t="n">
-        <v>0.18</v>
+        <v>-0.91</v>
       </c>
       <c r="L65" t="n">
         <v>5.5</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>6.86</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>217</v>
+        <v>209.26</v>
       </c>
       <c r="I66" t="n">
         <v>212.0529357014593</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>38</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K66" t="n">
-        <v>9.6</v>
+        <v>5.69</v>
       </c>
       <c r="L66" t="n">
         <v>1.24</v>
       </c>
       <c r="M66" t="n">
-        <v>1.52</v>
+        <v>2.76</v>
       </c>
       <c r="N66" t="n">
-        <v>2.24</v>
+        <v>3.22</v>
       </c>
       <c r="O66" t="n">
         <v>1.02</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.69</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46233.55208333334</v>
+        <v>46234.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>186.99</v>
+        <v>189.26</v>
       </c>
       <c r="I67" t="n">
         <v>188.3703646476953</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>73.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K67" t="n">
-        <v>10.64</v>
+        <v>9.56</v>
       </c>
       <c r="L67" t="n">
         <v>4.64</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>4.2</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46246.55208333334</v>
+        <v>46247.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>185.49</v>
+        <v>183.75</v>
       </c>
       <c r="I68" t="n">
         <v>184.6683003803872</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.99</v>
+        <v>-2.91</v>
       </c>
       <c r="L68" t="n">
-        <v>2.99</v>
+        <v>3.06</v>
       </c>
       <c r="M68" t="n">
         <v>0.2</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>4.98</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46260.38541666666</v>
+        <v>46260.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>185.71</v>
+        <v>189.45</v>
       </c>
       <c r="I69" t="n">
         <v>188.8333525998175</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.07</v>
+        <v>-3.1</v>
       </c>
       <c r="L69" t="n">
-        <v>1.92</v>
+        <v>3.37</v>
       </c>
       <c r="M69" t="n">
         <v>1.11</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>4.88</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>185.69</v>
+        <v>178.54</v>
       </c>
       <c r="I70" t="n">
         <v>182.1693437247043</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.98</v>
+        <v>-5.76</v>
       </c>
       <c r="L70" t="n">
-        <v>4.84</v>
+        <v>6.51</v>
       </c>
       <c r="M70" t="n">
         <v>1.37</v>
       </c>
       <c r="N70" t="n">
-        <v>2.28</v>
+        <v>3.93</v>
       </c>
       <c r="O70" t="n">
         <v>2.71</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,12 @@
       <c r="Q71" t="n">
         <v>34</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7450,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>73.2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7480,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44.9</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="11">
@@ -6683,7 +7540,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.64</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7550,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.73</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7560,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.52</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7570,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.84</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7580,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.5</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.6</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7600,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.31</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7610,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.66</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7620,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -6783,7 +7640,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="25">
@@ -6803,7 +7660,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.97</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7670,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.91</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7680,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
